--- a/output/pdf_financials_xlsx/SVP.H.xlsx
+++ b/output/pdf_financials_xlsx/SVP.H.xlsx
@@ -5852,28 +5852,28 @@
         <v>0.043042</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.03744</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.03744</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.043012</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.043012</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.043012</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.043012</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.043012</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.043012</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -5881,16 +5881,16 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.043012</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.043012</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.043012</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.043012</v>
       </c>
     </row>
     <row r="93">
@@ -9176,7 +9176,11 @@
           <t>Reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -10296,7 +10300,11 @@
           <t>Reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11256,7 +11264,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11926,7 +11938,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -12800,7 +12816,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -13362,7 +13382,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SVP.H.xlsx
+++ b/output/pdf_financials_xlsx/SVP.H.xlsx
@@ -2355,37 +2355,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.030825</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.150534</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.006127</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.011377</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.0009120000000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00066</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.04551</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.018195</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.00395</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2393,16 +2393,16 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.003597</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.002042</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.000271</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.058998</v>
       </c>
     </row>
     <row r="35">
@@ -2469,37 +2469,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.030825</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.150534</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.006127</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.011377</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.0009120000000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00066</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.04551</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.018195</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.00395</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -2507,16 +2507,16 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.003597</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.002042</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.000271</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.058998</v>
       </c>
     </row>
     <row r="37">
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.030825</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.130534</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -3168,22 +3168,22 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.006617</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.0009120000000000001</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.00066</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.04551</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.018195</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.00395</v>
+        <v>0</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -3191,16 +3191,16 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.00491</v>
+        <v>0.001313</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.003355</v>
+        <v>0.001313</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.001584</v>
+        <v>0.001313</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.060311</v>
+        <v>0.001313</v>
       </c>
     </row>
     <row r="49">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -28850,7 +28850,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -30092,7 +30092,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
